--- a/docs/Requirements-Traceability-Matrix.xlsx
+++ b/docs/Requirements-Traceability-Matrix.xlsx
@@ -22,9 +22,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD-MMM-YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD-MMM-YYYY"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -81,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -89,7 +88,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -98,8 +97,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -646,7 +649,8 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>API register exists (name, email, phone, password, user_type, institution). Missing: DOB/age band, gender, region, consent/guardian, registration reference, Pending Verification status (currently auto-verified + token issued), inactive-institution check, member-facing registration UI in repo.</t>
+          <t>API register exists (name, email, phone, password, user_type, institution). Missing: DOB/age band, gender, region, consent/guardian, registration reference, Pending Verification status (currently auto-verified + token issued), inactive-institution check, member-facing registration UI in repo.
+UPDATE 16-Oct-2026: Web + API registration with Pending Verification and reference number (branch feat/laravel13-livewire-tailwind). Still missing: DOB/age band, guardian consent capture, region, confirmation notification.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -689,7 +693,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -737,7 +741,8 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>No implementation in prototype.</t>
+          <t>No implementation in prototype.
+UPDATE 16-Oct-2026: Verification queue with filters, approve/reject with reason, officer and time recorded. Still missing: coordinator/patron scope, applicant notification.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -780,7 +785,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -828,7 +833,8 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>No implementation in prototype.</t>
+          <t>No implementation in prototype.
+UPDATE 16-Oct-2026: Approval activates the account and issues an interim membership number. Still missing: notification, final number format (D-03).</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -867,7 +873,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -915,7 +921,8 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Email+password login with Sanctum token and permission list; single-session. Missing: phone login, lockout/rate limit, login audit, token expiry, suspended-status enforcement, MFA for staff.</t>
+          <t>Email+password login with Sanctum token and permission list; single-session. Missing: phone login, lockout/rate limit, login audit, token expiry, suspended-status enforcement, MFA for staff.
+UPDATE 16-Oct-2026: Web sign-in by phone or email with rate limiting and status checks; API login blocks non-active accounts. Still missing: login audit, token expiry, staff MFA.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -958,7 +965,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -10062,10 +10069,10 @@
           <t>S0–S1</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="8" t="n">
         <v>46328</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="8" t="n">
         <v>46353</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -10113,10 +10120,10 @@
           <t>S2–S6</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="8" t="n">
         <v>46356</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="8" t="n">
         <v>46444</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -10164,10 +10171,10 @@
           <t>S7–S9</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="8" t="n">
         <v>46447</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="8" t="n">
         <v>46486</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -10215,10 +10222,10 @@
           <t>S10–S13</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="8" t="n">
         <v>46489</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="8" t="n">
         <v>46542</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10266,10 +10273,10 @@
           <t>S14–S17</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="8" t="n">
         <v>46545</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="8" t="n">
         <v>46598</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10317,10 +10324,10 @@
           <t>S18–S19</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="8" t="n">
         <v>46601</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="8" t="n">
         <v>46626</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10368,10 +10375,10 @@
           <t>S20–S21</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="8" t="n">
         <v>46629</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="8" t="n">
         <v>46654</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10411,8 +10418,8 @@
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2">
         <f>SUM(G2:G8)</f>
@@ -10500,10 +10507,10 @@
           <t>S0</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="9" t="n">
         <v>46328</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="9" t="n">
         <v>46339</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -10523,10 +10530,10 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="9" t="n">
         <v>46342</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="9" t="n">
         <v>46353</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -10546,10 +10553,10 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="9" t="n">
         <v>46356</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="9" t="n">
         <v>46367</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -10569,10 +10576,10 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="9" t="n">
         <v>46391</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="9" t="n">
         <v>46402</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -10592,10 +10599,10 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="9" t="n">
         <v>46405</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="9" t="n">
         <v>46416</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -10615,10 +10622,10 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="9" t="n">
         <v>46419</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="9" t="n">
         <v>46430</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -10638,10 +10645,10 @@
           <t>S6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="9" t="n">
         <v>46433</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="9" t="n">
         <v>46444</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -10661,10 +10668,10 @@
           <t>S7</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="9" t="n">
         <v>46447</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="9" t="n">
         <v>46458</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -10684,10 +10691,10 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="9" t="n">
         <v>46461</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="9" t="n">
         <v>46472</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -10707,10 +10714,10 @@
           <t>S9</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="9" t="n">
         <v>46475</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="9" t="n">
         <v>46486</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -10730,10 +10737,10 @@
           <t>S10</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="9" t="n">
         <v>46489</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="9" t="n">
         <v>46500</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -10753,10 +10760,10 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="9" t="n">
         <v>46503</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="9" t="n">
         <v>46514</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -10776,10 +10783,10 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="9" t="n">
         <v>46517</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="9" t="n">
         <v>46528</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -10799,10 +10806,10 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="9" t="n">
         <v>46531</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="9" t="n">
         <v>46542</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -10822,10 +10829,10 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="9" t="n">
         <v>46545</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="9" t="n">
         <v>46556</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -10845,10 +10852,10 @@
           <t>S15</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="9" t="n">
         <v>46559</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="9" t="n">
         <v>46570</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -10868,10 +10875,10 @@
           <t>S16</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="9" t="n">
         <v>46573</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="9" t="n">
         <v>46584</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -10891,10 +10898,10 @@
           <t>S17</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="9" t="n">
         <v>46587</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="9" t="n">
         <v>46598</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -10914,10 +10921,10 @@
           <t>S18</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="9" t="n">
         <v>46601</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="9" t="n">
         <v>46612</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -10937,10 +10944,10 @@
           <t>S19</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="9" t="n">
         <v>46615</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="9" t="n">
         <v>46626</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -10960,10 +10967,10 @@
           <t>S20</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="9" t="n">
         <v>46629</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="9" t="n">
         <v>46640</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -10983,10 +10990,10 @@
           <t>S21</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="9" t="n">
         <v>46643</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="9" t="n">
         <v>46654</v>
       </c>
       <c r="D23" t="inlineStr">

--- a/docs/Requirements-Traceability-Matrix.xlsx
+++ b/docs/Requirements-Traceability-Matrix.xlsx
@@ -742,7 +742,8 @@
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>No implementation in prototype.
-UPDATE 16-Oct-2026: Verification queue with filters, approve/reject with reason, officer and time recorded. Still missing: coordinator/patron scope, applicant notification.</t>
+UPDATE 16-Oct-2026: Verification queue with filters, approve/reject with reason, officer and time recorded. Still missing: coordinator/patron scope, applicant notification.
+UPDATE 17-Oct-2026: Verification queue now scoped: patrons see and decide only their own institution; TRA officers need view_all_registrations. Still missing: region-scoped coordinators, applicant notification.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -1907,7 +1908,8 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Create institution with name, type, region, district. Missing: unique code, contacts, has_tax_club, status, duplicate check, created_by, region/district master data.</t>
+          <t>Create institution with name, type, region, district. Missing: unique code, contacts, has_tax_club, status, duplicate check, created_by, region/district master data.
+UPDATE 17-Oct-2026: Admin form + CSV import: category, 31-region list, district, contacts, generated code (e.g. DSM-S-0042), duplicate check, created_by, active on creation.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1946,7 +1948,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1996,8 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Update endpoint exists. Missing: audit history (before/after), identifier protection.</t>
+          <t>Update endpoint exists. Missing: audit history (before/after), identifier protection.
+UPDATE 17-Oct-2026: Edit form with code protected and duplicate check. Still missing: before/after audit log of field changes (shared Audit service).</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2033,7 +2036,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2084,8 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>No implementation in prototype.</t>
+          <t>No implementation in prototype.
+UPDATE 17-Oct-2026: Activate/deactivate with mandatory reason and status history; inactive institutions hidden from registration and the public API; members kept.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2120,7 +2124,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2172,8 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>No implementation in prototype.</t>
+          <t>No implementation in prototype.
+UPDATE 17-Oct-2026: Tax Club per institution, establishment date, status with reason, one active club per institution.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2207,7 +2212,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2260,8 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>No implementation in prototype.</t>
+          <t>No implementation in prototype.
+UPDATE 17-Oct-2026: Assign patron by phone (existing user or new staff account with one-time password), start date, end with reason, history kept, Patron role granted/removed. Still missing: notification to the patron (Notifications module).</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2294,7 +2300,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2439,8 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>List supports search by name and filter by type/region. Missing: district/status/club filters, patron/coordinator display, stats, scope-restricted results.</t>
+          <t>List supports search by name and filter by type/region. Missing: district/status/club filters, patron/coordinator display, stats, scope-restricted results.
+UPDATE 17-Oct-2026: Search by name/code/district; filters by category, region, status; shows Tax Club and patrons. Still missing: coordinator display and region-scoped results (INS-REQ06).</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2472,7 +2479,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2527,8 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>No implementation in prototype.</t>
+          <t>No implementation in prototype.
+UPDATE 17-Oct-2026: Per-institution active, waiting and alumni counts (staff excluded). Still missing: category breakdown and dashboard/report export.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2559,7 +2567,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>

--- a/docs/Requirements-Traceability-Matrix.xlsx
+++ b/docs/Requirements-Traceability-Matrix.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>

--- a/docs/Requirements-Traceability-Matrix.xlsx
+++ b/docs/Requirements-Traceability-Matrix.xlsx
@@ -1591,7 +1591,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>

--- a/docs/Requirements-Traceability-Matrix.xlsx
+++ b/docs/Requirements-Traceability-Matrix.xlsx
@@ -966,7 +966,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/Requirements-Traceability-Matrix.xlsx
+++ b/docs/Requirements-Traceability-Matrix.xlsx
@@ -2654,7 +2654,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/Requirements-Traceability-Matrix.xlsx
+++ b/docs/Requirements-Traceability-Matrix.xlsx
@@ -4932,7 +4932,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8875,7 +8875,7 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/Requirements-Traceability-Matrix.xlsx
+++ b/docs/Requirements-Traceability-Matrix.xlsx
@@ -3354,7 +3354,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
